--- a/data/trans_orig/Q04C1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Edad-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda</t>
+          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,65; 17,62</t>
+          <t>14,6; 17,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,12; 16,03</t>
+          <t>12,99; 15,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 16,45</t>
+          <t>14,31; 16,39</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,75</t>
+          <t>9,32; 12,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 12,41</t>
+          <t>9,67; 12,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 12,17</t>
+          <t>9,86; 12,2</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 12,99</t>
+          <t>10,6; 12,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,91; 12,52</t>
+          <t>10,92; 12,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,03; 12,51</t>
+          <t>11,01; 12,47</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 19,37</t>
+          <t>16,92; 19,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,67; 19,79</t>
+          <t>17,69; 19,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,68; 19,22</t>
+          <t>17,69; 19,26</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,08; 26,84</t>
+          <t>24,07; 26,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,59; 27,66</t>
+          <t>25,49; 27,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,18; 26,86</t>
+          <t>25,07; 26,75</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,95; 31,06</t>
+          <t>28,03; 31,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,15; 32,65</t>
+          <t>26,13; 32,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,63; 31,31</t>
+          <t>26,49; 31,15</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,82; 39,92</t>
+          <t>35,6; 39,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,07; 42,48</t>
+          <t>39,02; 42,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,29; 40,87</t>
+          <t>38,37; 40,84</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,58; 21,04</t>
+          <t>19,57; 20,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,74; 23,28</t>
+          <t>21,77; 23,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,98; 22,02</t>
+          <t>20,95; 22,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Edad-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>16,21</t>
+          <t>14,71</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>13,69</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,47</t>
+          <t>14,19</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 17,53</t>
+          <t>12,87; 16,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 15,98</t>
+          <t>12,24; 15,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 16,39</t>
+          <t>13,01; 15,36</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,96</t>
+          <t>10,78</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11,05</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>10,52</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 12,69</t>
+          <t>9,22; 12,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 12,46</t>
+          <t>8,98; 11,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 12,2</t>
+          <t>9,48; 11,58</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,74</t>
+          <t>11,15</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,71</t>
+          <t>11,26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,73</t>
+          <t>11,2</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,6; 12,91</t>
+          <t>10,04; 12,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,92; 12,52</t>
+          <t>10,47; 12,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,01; 12,47</t>
+          <t>10,56; 11,93</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,08</t>
+          <t>17,58</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,76</t>
+          <t>18,59</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,44</t>
+          <t>18,09</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 19,35</t>
+          <t>16,49; 18,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 19,66</t>
+          <t>17,71; 19,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 19,26</t>
+          <t>17,37; 18,82</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25,36</t>
+          <t>24,56</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26,53</t>
+          <t>25,92</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25,94</t>
+          <t>25,24</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,07; 26,84</t>
+          <t>23,18; 25,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,49; 27,49</t>
+          <t>24,99; 26,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,07; 26,75</t>
+          <t>24,45; 26,17</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29,58</t>
+          <t>28,96</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28,68</t>
+          <t>31,76</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28,98</t>
+          <t>30,38</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,03; 31,18</t>
+          <t>27,38; 30,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,13; 32,71</t>
+          <t>30,42; 33,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,49; 31,15</t>
+          <t>29,34; 31,45</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>37,88</t>
+          <t>37,23</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>40,66</t>
+          <t>40,31</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39,56</t>
+          <t>39,08</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,6; 39,84</t>
+          <t>35,27; 39,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,02; 42,18</t>
+          <t>38,73; 41,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,37; 40,84</t>
+          <t>37,86; 40,37</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>19,57</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22,43</t>
+          <t>21,55</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,45</t>
+          <t>20,58</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,57; 20,98</t>
+          <t>18,91; 20,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,77; 23,3</t>
+          <t>20,94; 22,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,95; 22,1</t>
+          <t>20,15; 21,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Edad-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
+          <t>Tiempo medio en años que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
